--- a/documents_new/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents_new/WeValue_현장ACD_메신저템플릿.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lds85\Desktop\임덕수\git\2026-QI\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\임덕수\2026-QI\documents_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183160A4-6E50-4ED4-899D-6C382CB6E404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CE3061-A498-4ED8-9BD9-C696DC287FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="소통메신저 양식 자동완성" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <author>rahee</author>
   </authors>
   <commentList>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{90FACE3A-7ACC-4375-84D2-A8192ABCBC10}">
+    <comment ref="L4" authorId="0" shapeId="0" xr:uid="{90FACE3A-7ACC-4375-84D2-A8192ABCBC10}">
       <text>
         <r>
           <rPr>
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="114">
   <si>
     <t>D(완료)</t>
   </si>
@@ -257,10 +257,6 @@
   </si>
   <si>
     <t>교수이름</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>월일(MMDD)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -273,10 +269,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>시간(HHMM)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>시간
 (HHMM)</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -315,10 +307,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>가나다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>[CHEMO]</t>
   </si>
   <si>
@@ -403,14 +391,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>처방확인</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>박OO</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>야간이음기록</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -471,18 +451,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>KJS</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>이름</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>이OO</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>팀</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -508,9 +476,6 @@
   </si>
   <si>
     <t>141-MH</t>
-  </si>
-  <si>
-    <t>141-MH</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -540,12 +505,6 @@
   <si>
     <t>병동소속</t>
     <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>나이트</t>
-  </si>
-  <si>
-    <t>B</t>
   </si>
   <si>
     <t>CASE ID</t>
@@ -637,6 +596,10 @@
   <si>
     <t>지금(핵심)
 근거(데이터)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름(본인)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -649,7 +612,7 @@
     <numFmt numFmtId="177" formatCode="hhmm"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -683,6 +646,7 @@
     <font>
       <sz val="11"/>
       <name val="Consolas"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="8"/>
@@ -701,14 +665,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -717,14 +673,6 @@
     <font>
       <b/>
       <sz val="24"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -754,14 +702,64 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="0"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -785,12 +783,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -801,14 +793,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -933,11 +919,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -963,103 +964,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1068,56 +1018,95 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1459,466 +1448,426 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:L21"/>
+  <dimension ref="B1:L20"/>
   <sheetFormatPr defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.25" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.25" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.25" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="96.125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="100.25" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-    </row>
-    <row r="2" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-    </row>
-    <row r="3" spans="2:12" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="12" t="s">
+      <c r="B1" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+    </row>
+    <row r="2" spans="2:12" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B2" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+    </row>
+    <row r="3" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+    </row>
+    <row r="4" spans="2:12" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B4" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="51"/>
+      <c r="E4" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="51"/>
+      <c r="G4" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="51"/>
+      <c r="I4" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="53" t="str">
+        <f>"["&amp;D4&amp;"/"&amp;F4&amp;"/"&amp;H4&amp;"] "&amp;J4</f>
+        <v xml:space="preserve">[//] </v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B5" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="58">
-        <v>92</v>
-      </c>
-      <c r="E3" s="12" t="s">
+      <c r="D5" s="51"/>
+      <c r="E5" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="58" t="s">
-        <v>99</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="H3" s="58" t="s">
-        <v>100</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K3" s="13"/>
-      <c r="L3" s="15" t="str">
-        <f>"["&amp;D3&amp;"/"&amp;F3&amp;"/"&amp;H3&amp;"] "&amp;J3</f>
-        <v>[92/나이트/B] 이OO</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="58" t="s">
+      <c r="F5" s="54"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="J5" s="51"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="53" t="str">
+        <f>"["&amp;D5&amp;"/"&amp;G5&amp;"] "&amp;J5</f>
+        <v xml:space="preserve">[/] </v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="14"/>
+    </row>
+    <row r="7" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="37"/>
-      <c r="I4" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K4" s="13"/>
-      <c r="L4" s="15" t="str">
-        <f>"["&amp;D4&amp;"/"&amp;G4&amp;"] "&amp;J4</f>
-        <v>[141-MH/KJS] 이OO</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="18"/>
-    </row>
-    <row r="6" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-    </row>
-    <row r="7" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="19" t="s">
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="16"/>
+    </row>
+    <row r="8" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="C8" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="D8" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="E8" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="F8" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="47"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
+      <c r="K8" s="47"/>
+      <c r="L8" s="16"/>
+    </row>
+    <row r="9" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="56" t="str">
+        <f ca="1">"["&amp;B9&amp;"]-["&amp;C9&amp;"]-["&amp;D9&amp;"]-["&amp;E9&amp;"]-["&amp;TEXT(TEXT(NOW(), "mmdd"),"0000")&amp;"]-["&amp;TEXT(TEXT(NOW(), "hhmm"),"0000")&amp;"]"</f>
+        <v>[]-[]-[]-[]-[0404]-[2333]</v>
+      </c>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="16"/>
+    </row>
+    <row r="10" spans="2:12" s="9" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+    </row>
+    <row r="11" spans="2:12" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" s="30"/>
+      <c r="G11" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-    </row>
-    <row r="8" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="20">
-        <v>1311</v>
-      </c>
-      <c r="E8" s="20">
-        <v>12345678</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="21" t="str">
-        <f ca="1">TEXT(NOW(), "mmdd")</f>
-        <v>0329</v>
-      </c>
-      <c r="I8" s="22" t="str">
-        <f ca="1">TEXT(NOW(), "hhmm")</f>
-        <v>2340</v>
-      </c>
-      <c r="J8" s="41" t="str">
-        <f ca="1">"["&amp;D8&amp;"]-["&amp;E8&amp;"]-["&amp;F8&amp;"]-["&amp;G8&amp;"]-["&amp;TEXT(H8,"0000")&amp;"]-["&amp;TEXT(I8,"0000")&amp;"]"</f>
-        <v>[1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340]</v>
-      </c>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
-    </row>
-    <row r="9" spans="2:12" s="9" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-    </row>
-    <row r="10" spans="2:12" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="19" t="s">
+    </row>
+    <row r="12" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="32"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="36" t="str">
+        <f ca="1">C12&amp;IF($F$9="","", "[A]"&amp;$F$9&amp;" / "&amp;E12&amp;" / 요청:"&amp;G12&amp;" / "&amp;D12)</f>
+        <v xml:space="preserve">[CVR][A][]-[]-[]-[]-[0404]-[2333] /  / 요청: / </v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="32"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="36" t="str">
+        <f ca="1">C13&amp;IF($F$9="","", "[A]"&amp;$F$9&amp;" / "&amp;E13&amp;" / 요청:"&amp;G13&amp;" / "&amp;D13)</f>
+        <v xml:space="preserve">[검사전/후][A][]-[]-[]-[]-[0404]-[2333] /  / 요청: / </v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="36" t="str">
+        <f ca="1">IF($F$9="","", "[C]"&amp;$F$9&amp;" / "&amp;IF(H14="","{사유코드}",H14)&amp;" / 다음확인 "&amp;I14&amp;" (전화 1회 후)")</f>
+        <v>[C][]-[]-[]-[]-[0404]-[2333] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="36" t="str">
+        <f ca="1">IF($F$9="","", "[C]"&amp;$F$9&amp;" / "&amp;IF(H15="","{사유코드}",H15)&amp;" / 다음확인 "&amp;I15&amp;" (전화 1회 후)")</f>
+        <v>[C][]-[]-[]-[]-[0404]-[2333] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="36" t="str">
+        <f ca="1">IF($F$9="","", "[D]"&amp;$F$9&amp;" / 결과:"&amp;E16&amp;" / 현재:"&amp;J16&amp;" / F/U:"&amp;K16)</f>
+        <v>[D][]-[]-[]-[]-[0404]-[2333] / 결과: / 현재: / F/U:</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="39" t="str">
+        <f ca="1">IF($F$9="","", "(보고)"&amp;$F$9&amp;"/"&amp;E17&amp;IF(E17="","","/")&amp;"12")</f>
+        <v>(보고)[]-[]-[]-[]-[0404]-[2333]/12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" s="9" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="22"/>
+    </row>
+    <row r="19" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="47"/>
-      <c r="G10" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="K10" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="28">
-        <v>10</v>
-      </c>
-      <c r="E11" s="44"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="29" t="str">
-        <f ca="1">C11&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / "&amp;E11&amp;" / 요청:"&amp;G11&amp;" / "&amp;D11)</f>
-        <v>[CVR][A][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340] /  / 요청: / 10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="59" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="28">
-        <v>10</v>
-      </c>
-      <c r="E12" s="44"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="29" t="str">
-        <f ca="1">C12&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / "&amp;E12&amp;" / 요청:"&amp;G12&amp;" / "&amp;D12)</f>
-        <v>[검사전/후][A][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340] /  / 요청: / 10</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="29" t="str">
-        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H13="","{사유코드}",H13)&amp;" / 다음확인 "&amp;I13&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="19" t="s">
+      <c r="C19" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="41"/>
+      <c r="E19" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="40"/>
+    </row>
+    <row r="20" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="29" t="str">
-        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H14="","{사유코드}",H14)&amp;" / 다음확인 "&amp;I14&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="K15" s="28"/>
-      <c r="L15" s="29" t="str">
-        <f ca="1">IF($J$8="","", "[D]"&amp;$J$8&amp;" / 결과:"&amp;E15&amp;" / 현재:"&amp;J15&amp;" / F/U:"&amp;K15)</f>
-        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340] / 결과: / 현재:처방확인 / F/U:</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="50"/>
-      <c r="L16" s="51" t="str">
-        <f ca="1">IF($J$8="","", "(보고)"&amp;$J$8&amp;"/"&amp;E16&amp;IF(E16="","","/")&amp;"12")</f>
-        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340]/12</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" s="9" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="57"/>
-    </row>
-    <row r="18" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54" t="s">
-        <v>69</v>
-      </c>
-      <c r="J18" s="54"/>
-      <c r="K18" s="54"/>
-      <c r="L18" s="52"/>
-    </row>
-    <row r="19" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="29" t="str">
-        <f ca="1">IF($J$8="","", "[A][야간이음기록]"&amp;$J$8&amp;"/지금:"&amp;C19&amp;"/조치:"&amp;E19&amp;"/[D]"&amp;E19&amp;I19)</f>
-        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340]/지금:/조치:/[D]</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="36" t="str">
+        <f ca="1">IF($F$9="","", "[A][야간이음기록]"&amp;$F$9&amp;"/지금:"&amp;C20&amp;"/조치:"&amp;E20&amp;"/[D]"&amp;E20&amp;I20)</f>
+        <v>[A][야간이음기록][]-[]-[]-[]-[0404]-[2333]/지금:/조치:/[D]</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="E10:F10"/>
+  <mergeCells count="17">
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="F8:K8"/>
+    <mergeCell ref="F9:K9"/>
     <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="C19:D19"/>
     <mergeCell ref="E19:H19"/>
     <mergeCell ref="I19:K19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B6:L6"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B3:L3"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="C11:D12">
+  <conditionalFormatting sqref="C12:D13">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>C11=12</formula>
+      <formula>C12=12</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C11=4</formula>
+      <formula>C12=4</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>C11=10</formula>
+      <formula>C12=10</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1931,67 +1880,67 @@
           <x14:formula1>
             <xm:f>'02_코드목록'!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D16:D17 D11:D12</xm:sqref>
+          <xm:sqref>D17:D18 D12:D13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$B$2:$B$14</xm:f>
           </x14:formula1>
-          <xm:sqref>H15</xm:sqref>
+          <xm:sqref>H16</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{72FFAC11-A338-427E-AF73-F7D83A85893C}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$J$2:$J$4</xm:f>
           </x14:formula1>
-          <xm:sqref>E16:E17</xm:sqref>
+          <xm:sqref>E17:E18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{0D061B27-2ED0-4A89-8EF3-BCF08CD5E27F}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>H13</xm:sqref>
+          <xm:sqref>H14</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{06472377-7060-4FB5-A3C2-0B85F9411171}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$D$2</xm:f>
           </x14:formula1>
-          <xm:sqref>H14</xm:sqref>
+          <xm:sqref>H15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0BB3FC94-3ED2-4C84-A3ED-2F30071EDD5F}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$B$36:$B$38</xm:f>
           </x14:formula1>
-          <xm:sqref>F3</xm:sqref>
+          <xm:sqref>F4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{520AB831-8948-4772-A944-BFC6D5A572B3}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$E$36:$E$40</xm:f>
           </x14:formula1>
-          <xm:sqref>H3</xm:sqref>
+          <xm:sqref>H4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F832BF57-460C-4480-8BA8-EBC99E7230DB}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$K$36:$K$39</xm:f>
           </x14:formula1>
-          <xm:sqref>D3</xm:sqref>
+          <xm:sqref>D4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{33E7ADC8-529F-4927-AAE9-C790AFD91F36}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$H$36:$H$41</xm:f>
           </x14:formula1>
-          <xm:sqref>D4</xm:sqref>
+          <xm:sqref>D5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{54F24218-F1A5-4C39-A88F-EBBD79DE5CE8}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$L$16:$L$28</xm:f>
           </x14:formula1>
-          <xm:sqref>C12</xm:sqref>
+          <xm:sqref>C13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5ED51441-025F-4310-B118-7A6E4E87943E}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$L$2:$L$11</xm:f>
           </x14:formula1>
-          <xm:sqref>C11</xm:sqref>
+          <xm:sqref>C12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2023,10 +1972,10 @@
         <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>6</v>
@@ -2034,12 +1983,11 @@
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="J1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L1" s="49" t="s">
-        <v>119</v>
-      </c>
-      <c r="M1" s="49"/>
+        <v>33</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
@@ -2049,22 +1997,22 @@
         <v>7</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+        <v>56</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
       <c r="J2" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -2074,18 +2022,18 @@
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
       <c r="J3" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -2095,18 +2043,18 @@
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
       <c r="J4" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K4" s="6"/>
       <c r="L4" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -2114,10 +2062,10 @@
         <v>10</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -2125,10 +2073,10 @@
         <v>11</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -2136,10 +2084,10 @@
         <v>12</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -2147,10 +2095,10 @@
         <v>13</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -2158,10 +2106,10 @@
         <v>14</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -2169,10 +2117,10 @@
         <v>15</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -2180,10 +2128,10 @@
         <v>16</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -2203,104 +2151,104 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="L16" s="48" t="s">
-        <v>103</v>
+      <c r="L16" s="19" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L17" s="48" t="s">
-        <v>104</v>
+      <c r="L17" s="19" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L18" s="48" t="s">
-        <v>105</v>
+      <c r="L18" s="19" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L19" s="48" t="s">
-        <v>106</v>
+      <c r="L19" s="19" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L20" s="48" t="s">
-        <v>108</v>
+      <c r="L20" s="19" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L21" s="48" t="s">
-        <v>109</v>
+      <c r="L21" s="19" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L22" s="48" t="s">
-        <v>110</v>
+      <c r="L22" s="19" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L23" s="48" t="s">
-        <v>111</v>
+      <c r="L23" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="11:12" x14ac:dyDescent="0.3">
       <c r="K24" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="L24" s="48" t="s">
-        <v>112</v>
+        <v>106</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L25" s="48" t="s">
-        <v>113</v>
+      <c r="L25" s="19" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L26" s="48" t="s">
-        <v>114</v>
+      <c r="L26" s="19" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L27" s="48" t="s">
-        <v>115</v>
+      <c r="L27" s="19" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="11:12" x14ac:dyDescent="0.3">
       <c r="K28" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="L28" s="48" t="s">
-        <v>116</v>
+        <v>106</v>
+      </c>
+      <c r="L28" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="K36" s="4">
         <v>92</v>
@@ -2308,13 +2256,13 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H37" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="K37" s="4">
         <v>131</v>
@@ -2322,13 +2270,13 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="K38" s="4">
         <v>141</v>
@@ -2336,10 +2284,10 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E39" s="4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="K39" s="4">
         <v>142</v>
@@ -2347,15 +2295,15 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E40" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H41" s="4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/documents_new/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents_new/WeValue_현장ACD_메신저템플릿.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\임덕수\2026-QI\documents_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CE3061-A498-4ED8-9BD9-C696DC287FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959C84DE-99DF-4278-9482-7612D67F0130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="113">
   <si>
     <t>D(완료)</t>
   </si>
@@ -529,9 +529,6 @@
   <si>
     <t>[수술전/후]</t>
     <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>[검사전/후]</t>
   </si>
   <si>
     <t>[검사전/후]</t>
@@ -740,7 +737,11 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -748,15 +749,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1030,31 +1025,13 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1067,9 +1044,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1107,6 +1081,27 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1482,81 +1477,81 @@
       <c r="L1" s="24"/>
     </row>
     <row r="2" spans="2:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
     </row>
     <row r="3" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
     </row>
     <row r="4" spans="2:12" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="50" t="s">
+      <c r="D4" s="44"/>
+      <c r="E4" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="51"/>
-      <c r="G4" s="50" t="s">
+      <c r="F4" s="44"/>
+      <c r="G4" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="51"/>
-      <c r="I4" s="52" t="s">
-        <v>113</v>
-      </c>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="53" t="str">
+      <c r="H4" s="44"/>
+      <c r="I4" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" s="44"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="46" t="str">
         <f>"["&amp;D4&amp;"/"&amp;F4&amp;"/"&amp;H4&amp;"] "&amp;J4</f>
         <v xml:space="preserve">[//] </v>
       </c>
     </row>
     <row r="5" spans="2:12" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C5" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="51"/>
-      <c r="E5" s="54" t="s">
+      <c r="D5" s="44"/>
+      <c r="E5" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="54"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="52" t="s">
-        <v>113</v>
-      </c>
-      <c r="J5" s="51"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="53" t="str">
+      <c r="F5" s="47"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" s="44"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="46" t="str">
         <f>"["&amp;D5&amp;"/"&amp;G5&amp;"] "&amp;J5</f>
         <v xml:space="preserve">[/] </v>
       </c>
@@ -1575,57 +1570,57 @@
       <c r="L6" s="14"/>
     </row>
     <row r="7" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
       <c r="L7" s="16"/>
     </row>
     <row r="8" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="46" t="s">
+      <c r="E8" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
-      <c r="K8" s="47"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
       <c r="L8" s="16"/>
     </row>
     <row r="9" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="56" t="str">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="49" t="str">
         <f ca="1">"["&amp;B9&amp;"]-["&amp;C9&amp;"]-["&amp;D9&amp;"]-["&amp;E9&amp;"]-["&amp;TEXT(TEXT(NOW(), "mmdd"),"0000")&amp;"]-["&amp;TEXT(TEXT(NOW(), "hhmm"),"0000")&amp;"]"</f>
-        <v>[]-[]-[]-[]-[0404]-[2333]</v>
-      </c>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
+        <v>[]-[]-[]-[]-[0404]-[2351]</v>
+      </c>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
       <c r="L9" s="16"/>
     </row>
     <row r="10" spans="2:12" s="9" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1646,13 +1641,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>2</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F11" s="30"/>
       <c r="G11" s="27" t="s">
@@ -1676,42 +1671,38 @@
     </row>
     <row r="12" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="35"/>
+        <v>110</v>
+      </c>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="53"/>
       <c r="H12" s="27"/>
       <c r="I12" s="27"/>
       <c r="J12" s="27"/>
       <c r="K12" s="27"/>
-      <c r="L12" s="36" t="str">
+      <c r="L12" s="31" t="str">
         <f ca="1">C12&amp;IF($F$9="","", "[A]"&amp;$F$9&amp;" / "&amp;E12&amp;" / 요청:"&amp;G12&amp;" / "&amp;D12)</f>
-        <v xml:space="preserve">[CVR][A][]-[]-[]-[]-[0404]-[2333] /  / 요청: / </v>
+        <v xml:space="preserve">[A][]-[]-[]-[]-[0404]-[2351] /  / 요청: / </v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="35"/>
+        <v>109</v>
+      </c>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="53"/>
       <c r="H13" s="27"/>
       <c r="I13" s="27"/>
       <c r="J13" s="27"/>
       <c r="K13" s="27"/>
-      <c r="L13" s="36" t="str">
+      <c r="L13" s="31" t="str">
         <f ca="1">C13&amp;IF($F$9="","", "[A]"&amp;$F$9&amp;" / "&amp;E13&amp;" / 요청:"&amp;G13&amp;" / "&amp;D13)</f>
-        <v xml:space="preserve">[검사전/후][A][]-[]-[]-[]-[0404]-[2333] /  / 요청: / </v>
+        <v xml:space="preserve">[A][]-[]-[]-[]-[0404]-[2351] /  / 요청: / </v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1723,13 +1714,13 @@
       <c r="E14" s="27"/>
       <c r="F14" s="27"/>
       <c r="G14" s="27"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="35"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="53"/>
       <c r="J14" s="27"/>
       <c r="K14" s="27"/>
-      <c r="L14" s="36" t="str">
+      <c r="L14" s="31" t="str">
         <f ca="1">IF($F$9="","", "[C]"&amp;$F$9&amp;" / "&amp;IF(H14="","{사유코드}",H14)&amp;" / 다음확인 "&amp;I14&amp;" (전화 1회 후)")</f>
-        <v>[C][]-[]-[]-[]-[0404]-[2333] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][]-[]-[]-[]-[0404]-[2351] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1741,13 +1732,13 @@
       <c r="E15" s="27"/>
       <c r="F15" s="27"/>
       <c r="G15" s="27"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="35"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="53"/>
       <c r="J15" s="27"/>
       <c r="K15" s="27"/>
-      <c r="L15" s="36" t="str">
+      <c r="L15" s="31" t="str">
         <f ca="1">IF($F$9="","", "[C]"&amp;$F$9&amp;" / "&amp;IF(H15="","{사유코드}",H15)&amp;" / 다음확인 "&amp;I15&amp;" (전화 1회 후)")</f>
-        <v>[C][]-[]-[]-[]-[0404]-[2333] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][]-[]-[]-[]-[0404]-[2351] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1756,34 +1747,34 @@
       </c>
       <c r="C16" s="27"/>
       <c r="D16" s="27"/>
-      <c r="E16" s="32"/>
+      <c r="E16" s="50"/>
       <c r="F16" s="27"/>
       <c r="G16" s="27"/>
       <c r="H16" s="27"/>
       <c r="I16" s="27"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="36" t="str">
+      <c r="J16" s="55"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="31" t="str">
         <f ca="1">IF($F$9="","", "[D]"&amp;$F$9&amp;" / 결과:"&amp;E16&amp;" / 현재:"&amp;J16&amp;" / F/U:"&amp;K16)</f>
-        <v>[D][]-[]-[]-[]-[0404]-[2333] / 결과: / 현재: / F/U:</v>
+        <v>[D][]-[]-[]-[]-[0404]-[2351] / 결과: / 현재: / F/U:</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="39" t="str">
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="33" t="str">
         <f ca="1">IF($F$9="","", "(보고)"&amp;$F$9&amp;"/"&amp;E17&amp;IF(E17="","","/")&amp;"12")</f>
-        <v>(보고)[]-[]-[]-[]-[0404]-[2333]/12</v>
+        <v>(보고)[]-[]-[]-[]-[0404]-[2351]/12</v>
       </c>
     </row>
     <row r="18" spans="2:12" s="9" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1800,42 +1791,42 @@
       <c r="L18" s="22"/>
     </row>
     <row r="19" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="42" t="s">
+      <c r="D19" s="35"/>
+      <c r="E19" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42" t="s">
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="40"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="34"/>
     </row>
     <row r="20" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="36" t="str">
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="56"/>
+      <c r="L20" s="31" t="str">
         <f ca="1">IF($F$9="","", "[A][야간이음기록]"&amp;$F$9&amp;"/지금:"&amp;C20&amp;"/조치:"&amp;E20&amp;"/[D]"&amp;E20&amp;I20)</f>
-        <v>[A][야간이음기록][]-[]-[]-[]-[0404]-[2333]/지금:/조치:/[D]</v>
+        <v>[A][야간이음기록][]-[]-[]-[]-[0404]-[2351]/지금:/조치:/[D]</v>
       </c>
     </row>
   </sheetData>
@@ -1986,7 +1977,7 @@
         <v>33</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -2154,7 +2145,7 @@
         <v>56</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -2179,53 +2170,53 @@
     </row>
     <row r="20" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L20" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L21" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L22" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L23" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="11:12" x14ac:dyDescent="0.3">
       <c r="K24" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L24" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L25" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L26" s="19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L27" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="11:12" x14ac:dyDescent="0.3">
       <c r="K28" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L28" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
